--- a/Documentation/Feature Scoring Rubric/Feature_Scoring_Rubric.xlsx
+++ b/Documentation/Feature Scoring Rubric/Feature_Scoring_Rubric.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\iCloudDrive\Interactive Pet Marketplace\Best For\Feature Scoring Rubric\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Feature Scoring Rubric\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A861BDB0-29FC-4BC2-84C3-B09D5DD5DE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BEA515E-8226-4BFA-AB49-F40F77D0EEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="167">
   <si>
     <t>Interactive Pet Marketplace — Product Feature Scoring Criteria</t>
   </si>
   <si>
-    <t>Last updated: 2026-06-25  |  Source of truth for all product scoring. Update this file whenever feature definitions, anchors, or scoring scope change, and commit the new copy to Documentation/ in the repo.</t>
+    <t>Last updated: 2026-07-02  |  Source of truth for all product scoring. Update this file whenever feature definitions, anchors, or scoring scope change, and commit the new copy to Documentation/ in the repo.</t>
   </si>
   <si>
     <t>Feature</t>
@@ -236,14 +236,24 @@
     <t>Dementia suitability</t>
   </si>
   <si>
-    <t>Overall fit for memory care: simplicity, familiar form, calmness, safety</t>
-  </si>
-  <si>
-    <t>5 = most suitable for memory care. 1 = least suitable (complex, non-pet form, potentially distressing).</t>
-  </si>
-  <si>
-    <t>Score=1: Screen/AI device not designed for dementia care; complexity contradicts memory-care guidance.
-Score=5: Most-documented product in this market for dementia care; cited in Journal of Holistic Nursing (2022) — 63% less anxiety, 57% less agitation. Best suited to early/mid-stage dementia.</t>
+    <t>Overall fit for memory care, assessed via four sub-criteria: Simplicity (no memorized commands/phrases, minimal buttons or menus, no charging-status literacy required), Familiar Form (reuses 'Recognizable pet appearance' score), Calmness (predictable, non-jarring interaction; informed by 'Sound quality' and realism), and Safety (reuses 'Safety risk' score). Each score must be tagged in Notes with an Evidence Tier (see Score Type) reflecting the strength of dementia-specific support behind it.</t>
+  </si>
+  <si>
+    <t>1-5. EVIDENCE TIERS (determine max score): Tier A = independent peer-reviewed research specific to the product (no cap, full 1-5 range). Tier B = independent caregiver/facility evidence — verified reviews, news coverage, facility pilot reports; NOT manufacturer-published (capped at 4). Tier C = manufacturer marketing claims only, no independent verification (capped at 4, per Tim 7/2026 — raised from initial proposal of 3). Tier D = no dementia-specific evidence found; scored by sub-criteria judgment alone (capped at 3).</t>
+  </si>
+  <si>
+    <t>5 = most suitable for memory care (Tier A only). 1 = least suitable (complex, non-pet form, potentially distressing). Score = average of the four sub-criteria, then reduced if necessary to fit the Evidence Tier cap above. STATUS (2026-07-02): First-pass sub-criteria scores computed and applied to all 29 products as Tim's 'best effort' baseline. Tim is sourcing a dementia care consultant to review and validate/adjust these scores. Products in the 'Ai &amp; Robotic Pets' Type category (Product Matrix.xlsx) are excluded from memory-care-relevant Best For lists via a Type filter in the Best For Weighting Table — this handles category-level exclusion (app/camera/WiFi dependency) separately from the per-product Dementia Suitability score, since no single scoring column reliably identified all such products (e.g. Ruko scored low on AI level/Control/Privacy despite being an 'Ai &amp; Robotic Pets' type product).</t>
+  </si>
+  <si>
+    <t>ElliQ (Tier D — no product-specific dementia research; screen/AI complexity scored via sub-criteria)</t>
+  </si>
+  <si>
+    <t>Joy for All Companion Pet (Tier A)</t>
+  </si>
+  <si>
+    <t>Score=1: ElliQ — screen/AI device not designed for dementia care; complexity contradicts memory-care guidance (sub-criteria judgment, Tier D).
+Score=5: Joy for All — most-documented product in this market for dementia care; cited in Journal of Holistic Nursing (2022) — 63% less anxiety, 57% less agitation; best suited to early/mid-stage dementia (Tier A, independent peer-reviewed).
+METHODOLOGY ADOPTED 2026-07-02 (Tim-directed): Replaces prior undocumented single-score approach after review found only Joy for All had genuine research backing — all other in-between scores (e.g. Chongker MateCat Pro at 4) had no documented rationale trail. New approach requires an Evidence Tier tag on every score. MateCat Pro specifically reviewed: only evidence found was Chongker's own 'Robotic Pets for Dementia Care' marketing page (unverified consultant/specialist quotes, no named institution) plus one unrelated anecdotal blog mention — classified Tier C. MateCat Pro also has more operational complexity than Joy for All (voice wake phrases, autonomous sleep mode, battery-status meow alerts) which weighs against the Simplicity sub-criterion. Current score of 4 sits at the Tier C cap and was not changed. Full sub-criteria breakdown (Simplicity/Familiar Form/Calmness/Safety individually scored and averaged) has NOT yet been computed per-product — current scores are the pre-existing single-score values, now tagged with Evidence Tier but not yet re-derived from the four sub-criteria. This should be done as a follow-up, ideally informed by the incoming dementia consultant's feedback.</t>
   </si>
   <si>
     <t>Durability</t>
@@ -325,24 +335,6 @@
 Score=5: 22 actuators, SLAM navigation, walking/sitting/complex movement (Sony ERS-1000 documentation).</t>
   </si>
   <si>
-    <t>Noise sensitivity fit</t>
-  </si>
-  <si>
-    <t>Suitable for people startled by sudden sound or quiet environments</t>
-  </si>
-  <si>
-    <t>1 – 5
-(reversed:
-5 = quiet)</t>
-  </si>
-  <si>
-    <t>5 = fully silent or near-silent. 1 = loud/unpredictable sounds with no mute option.</t>
-  </si>
-  <si>
-    <t>Score=1: Documented loud motor and unrealistic meow; startling in quiet settings (Best Buy/Walmart reviews).
-Score=5: No vocalizations or sounds of any kind — fully silent.</t>
-  </si>
-  <si>
     <t>Price tier</t>
   </si>
   <si>
@@ -491,17 +483,23 @@
     <t>Sound quality</t>
   </si>
   <si>
-    <t>Whether sounds are soothing, realistic, or annoying. Absence of sound = 2 (neutral — not obnoxious, but not soothing either).</t>
-  </si>
-  <si>
-    <t>5 = therapeutic/realistic sounds. 3 = acceptable/average. 2 = no sounds (neutral). 1 = loud, repetitive, unrealistic — worst in class.</t>
-  </si>
-  <si>
-    <t>Score=1: Constant loud repetitive barking, no mute (pawsdynasty.com).
-Score=2: Products producing no sounds (e.g. Perfect Petzzz) — not obnoxious but not soothing.
+    <t>Whether sounds are soothing, realistic, or unsettling — including verified reports in retailer reviews (Amazon, Best Buy, Walmart) of a product startling users or being unsuitable for noise-sensitive/quiet environments. As of 2026-07, this feature absorbs the former 'Noise sensitivity fit' feature (eliminated as a separate row — overlapping scope). Products that produce no sound of any kind are scored N/A, not on the 1-5 scale.</t>
+  </si>
+  <si>
+    <t>1 - 5, or N/A if the product produces no sound of any kind</t>
+  </si>
+  <si>
+    <t>5 = therapeutic/realistic, calming sound. 3 = acceptable/average — audible motor noise but not distressing. 1 = loud, repetitive, unrealistic sound, OR multiple verified reviews document the product startling users / being unsuitable for sound-sensitive people or quiet environments (e.g. dementia care) — weight verified startle reports toward a 1 even if the sound itself is otherwise unremarkable. N/A = product makes no sound at all (silence is not scored on this feature — see Sound Level Control for mute/volume control, which is scored separately).</t>
+  </si>
+  <si>
+    <t>Budget motorized barking robot dogs (e.g. Liberty Imports/PowerTRC, ~$15)</t>
+  </si>
+  <si>
+    <t>Score=1: Constant loud repetitive barking, no mute (pawsdynasty.com). Startle-risk reviews (Best Buy/Walmart) documenting sudden/unpredictable sound as distressing for noise-sensitive users should also be weighted toward 1, even for products with otherwise passable sound quality.
 Score=3 mid-point: Joy for All Companion Pet — motor noise audible, sounds below realism standard, but has MUTE option (verified by direct product comparison June 2026).
 Score=4: Chongker Percy/MateCat line — noticeably better than Joy for All; 4-level volume; motor noise minimized (direct comparison June 2026).
-Score=5: PARO — vocalizations recorded from real harp seal pups, engineered for therapeutic effect.</t>
+Score=5: PARO — vocalizations recorded from real harp seal pups, engineered for therapeutic effect.
+N/A: reserved for products verified to produce zero sound output. NOTE (2026-07-01): Perfect Petzzz was previously (incorrectly) treated as a silent/no-sound anchor for this feature and for the now-eliminated Noise Sensitivity Fit feature. Tim has corrected this — Perfect Petzzz DOES produce sound and should be scored 1-5 like any other product, not N/A. The 8 Perfect Petzzz SKUs in Product_Feature_Scores.xlsx currently show Sound quality=2 under the old 'absence of sound = neutral' methodology and need to be re-scored under this updated methodology once the actual sound characteristics are documented.</t>
   </si>
   <si>
     <t>Tactile comfort</t>
@@ -1268,56 +1266,56 @@
         <v>67</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>54</v>
@@ -1326,21 +1324,21 @@
         <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>54</v>
@@ -1349,21 +1347,21 @@
         <v>13</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>14</v>
@@ -1372,21 +1370,21 @@
         <v>13</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>13</v>
@@ -1395,400 +1393,378 @@
         <v>47</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G22" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="G26" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="5" t="s">
+      <c r="F32" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="G32" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="5" t="s">
+      <c r="G34" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>166</v>
       </c>
     </row>
+    <row r="36" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
